--- a/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T16:54:59+00:00</t>
+    <t>2025-02-11T12:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -26652,7 +26652,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>102</v>
@@ -27337,7 +27337,7 @@
         <v>102</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>84</v>
@@ -27871,7 +27871,7 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>102</v>
@@ -28553,7 +28553,7 @@
         <v>85</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>84</v>
